--- a/5_svm/3_resultados/comparativa_splits_resultados.xlsx
+++ b/5_svm/3_resultados/comparativa_splits_resultados.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marco\Documentos\investigacion\machine_learning_idalina\5_svm\3_resultados\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E83B8E8F-DFB8-46AE-84AC-D14F2B9F29BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{107535D0-F9CE-4BD5-B49B-169B3CB8D94B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -424,6 +424,7 @@
     <col min="8" max="8" width="17.26953125" customWidth="1"/>
     <col min="9" max="9" width="21.81640625" customWidth="1"/>
     <col min="10" max="10" width="13.26953125" customWidth="1"/>
+    <col min="12" max="12" width="19.6328125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.35">
